--- a/DataTables/DetailText/剧情/009_01贾荃痰火扰心.xlsx
+++ b/DataTables/DetailText/剧情/009_01贾荃痰火扰心.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{024E4416-446E-47BF-ACAE-85B25521784A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C10E5F-DC6E-46F2-81A0-99A76BE3E363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="46">
   <si>
     <t>StoryID</t>
   </si>
@@ -161,7 +161,23 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Portrait/jia_quan/jia_quan.png</t>
+    <t>陆忠</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>大夫大夫！救命啊大夫！我家老爷要不行了！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>李东璧</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>出什么事了？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>我家老爷刚才在醉仙楼喝酒，突然就开始胡言乱语，神志不清了。</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -169,19 +185,65 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>陆忠</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>大夫大夫！救命啊大夫！我家老爷要不行了！</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>李东璧</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>出什么事了？</t>
+    <t>我是湖广首富！哈哈哈哈，我看谁再敢小看我！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>我有一单大买卖，天大的买卖！呕~</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>这不是贾老板吗，快把他抬过来。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Portrait/StoryNpc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>jia_quan/jia_quan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>_sick</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>sick</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -315,7 +377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -366,6 +428,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -748,7 +813,7 @@
         <v>33</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -828,7 +893,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
@@ -876,7 +941,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -887,7 +952,7 @@
         <v>30</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -898,7 +963,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>9</v>
@@ -907,7 +972,7 @@
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -918,15 +983,17 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="1"/>
+      <c r="H4" s="20" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
@@ -935,36 +1002,112 @@
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="20" t="s">
+        <v>40</v>
+      </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="1"/>
+      <c r="H5" s="20" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="2"/>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="1"/>
+      <c r="H6" s="20" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="3"/>
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="H7" s="20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
